--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486391_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486391_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6254</v>
+        <v>2.8625</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4249</v>
+        <v>1.789</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7995</v>
+        <v>1.0735</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9232</v>
+        <v>0.0682</v>
       </c>
       <c r="H2" t="n">
-        <v>2.433</v>
+        <v>-2.1655</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4902</v>
+        <v>2.2337</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8399</v>
+        <v>1.6684</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2484</v>
+        <v>-1.0521</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5915</v>
+        <v>2.7205</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9167</v>
+        <v>-1.6003</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8153</v>
+        <v>-1.1134</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1013</v>
+        <v>-0.4869</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5225</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>0.137</v>
+        <v>0.2938</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2824</v>
+        <v>0.0781</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4194</v>
+        <v>0.2157</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9123</v>
+        <v>0.9779</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.0422</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3307</v>
+        <v>2.4289</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5655</v>
+        <v>5.5367</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7653</v>
+        <v>-3.1077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0682</v>
+        <v>4.9232</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.1655</v>
+        <v>2.433</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2337</v>
+        <v>2.4902</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6684</v>
+        <v>7.8399</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0521</v>
+        <v>3.2484</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7205</v>
+        <v>4.5915</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6003</v>
+        <v>-2.9167</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1134</v>
+        <v>-0.8153</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4869</v>
+        <v>-2.1013</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2379</v>
+        <v>-0.0595</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1454</v>
+        <v>-0.1706</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0925</v>
+        <v>0.1111</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9779</v>
+        <v>-0.9123</v>
       </c>
       <c r="W3" t="n">
         <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.152</v>
+        <v>-2.0422</v>
       </c>
     </row>
     <row r="4">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6943</v>
+        <v>1.7444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1065</v>
+        <v>0.2182</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5878</v>
+        <v>1.5262</v>
       </c>
       <c r="G5" t="n">
         <v>-0.483</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3495</v>
+        <v>0.3996</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>-0.0336</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4949</v>
+        <v>0.4332</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3473</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6908</v>
+        <v>1.2631</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0447</v>
+        <v>-0.38</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7355</v>
+        <v>1.643</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0335</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2244</v>
+        <v>-0.2034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>-0.1382</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0273</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.7175</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1172</v>
+        <v>-0.0054</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0463</v>
+        <v>0.158</v>
       </c>
       <c r="F7" t="n">
         <v>-0.1635</v>
@@ -1000,10 +1000,10 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2175</v>
+        <v>-0.1057</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
         <v>-0.149</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.1769</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2971</v>
+        <v>1.7441</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1676</v>
+        <v>-1.921</v>
       </c>
       <c r="G8" t="n">
         <v>-0.156</v>
@@ -1078,13 +1078,13 @@
         <v>2.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5396</v>
+        <v>-0.846</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9589</v>
+        <v>-0.5119</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5807</v>
+        <v>-0.3341</v>
       </c>
       <c r="V8" t="n">
         <v>1.9127</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2973</v>
+        <v>-2.966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9878</v>
+        <v>-0.4651</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2851</v>
+        <v>-2.5009</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9047</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8244</v>
+        <v>1.1557</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0898</v>
+        <v>0.6369</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7346</v>
+        <v>0.5188</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4345</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2921</v>
+        <v>-3.5349</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1189</v>
+        <v>-0.4542</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1731</v>
+        <v>-3.0807</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8508</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2688</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2656</v>
+        <v>-0.0697</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5344</v>
+        <v>-0.4419</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0931</v>
+        <v>-5.9447</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9246</v>
+        <v>-5.807</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1685</v>
+        <v>-0.1377</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1061</v>
@@ -1312,13 +1312,13 @@
         <v>3.0451</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.204</v>
+        <v>-0.0556</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.0469</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0395</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3904</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.516499999999999</v>
+        <v>-2.516500000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>5.120600000000001</v>
+        <v>5.1204</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.6369</v>
+        <v>-7.637</v>
       </c>
       <c r="G12" t="n">
         <v>-3.538000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>18.4882</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5829999999999997</v>
+        <v>0.5827999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08390000000000009</v>
+        <v>-0.08399999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6669999999999999</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7363</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9932</v>
+        <v>7.9739</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5042</v>
+        <v>6.3925</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4889</v>
+        <v>1.5814</v>
       </c>
       <c r="G13" t="n">
         <v>5.9266</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2671</v>
+        <v>0.2478</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0016</v>
+        <v>0.094</v>
       </c>
       <c r="V13" t="n">
         <v>1.582</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1859</v>
+        <v>3.5405</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0538</v>
+        <v>4.5009</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8679</v>
+        <v>-0.9604</v>
       </c>
       <c r="G14" t="n">
         <v>1.4238</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0857</v>
+        <v>0.2689</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.411</v>
+        <v>0.0361</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3253</v>
+        <v>0.2328</v>
       </c>
       <c r="V14" t="n">
         <v>0.7602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6766</v>
+        <v>1.6343</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4757</v>
+        <v>0.5874</v>
       </c>
       <c r="F15" t="n">
-        <v>1.201</v>
+        <v>1.0468</v>
       </c>
       <c r="G15" t="n">
         <v>0.4984</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6663</v>
+        <v>-0.7087</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1184</v>
+        <v>-0.2725</v>
       </c>
       <c r="V15" t="n">
         <v>-0.113</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4093</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3488</v>
+        <v>0.0136</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0605</v>
+        <v>0.9064</v>
       </c>
       <c r="G16" t="n">
         <v>2.1452</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2037</v>
+        <v>-0.2857</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1286</v>
+        <v>-0.2067</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0751</v>
+        <v>-0.079</v>
       </c>
       <c r="V16" t="n">
         <v>-1.592</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4579</v>
+        <v>-0.1202</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8735</v>
+        <v>2.2029</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4156</v>
+        <v>-2.3231</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8149</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9677</v>
+        <v>0.3897</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0106</v>
+        <v>0.3401</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9772</v>
+        <v>-0.7814</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2765</v>
+        <v>-2.5202</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2536</v>
+        <v>1.7388</v>
       </c>
       <c r="G18" t="n">
-        <v>1.222</v>
+        <v>2.1705</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0069</v>
+        <v>-0.0121</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2152</v>
+        <v>2.1826</v>
       </c>
       <c r="J18" t="n">
-        <v>4.0359</v>
+        <v>2.5651</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3568</v>
+        <v>0.9188</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6791</v>
+        <v>1.6463</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8138</v>
+        <v>-0.3946</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3499</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4639</v>
+        <v>0.5362</v>
       </c>
       <c r="P18" t="n">
         <v>-3.4801</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.7852</v>
+        <v>-5.4377</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5207000000000001</v>
+        <v>-0.6633</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2656</v>
+        <v>-0.2127</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2551</v>
+        <v>-0.4506</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7602</v>
+        <v>1.1915</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1593</v>
+        <v>-0.9435</v>
       </c>
       <c r="E19" t="n">
         <v>1.3096</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4688</v>
+        <v>-2.2531</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3766</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3049</v>
+        <v>0.5206</v>
       </c>
       <c r="T19" t="n">
         <v>0.2656</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0393</v>
+        <v>0.2551</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.24</v>
+        <v>-1.1082</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8555</v>
+        <v>0.053</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6155</v>
+        <v>-1.1612</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1705</v>
+        <v>1.222</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0121</v>
+        <v>1.0069</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1826</v>
+        <v>0.2152</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5651</v>
+        <v>4.0359</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9188</v>
+        <v>1.3568</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6463</v>
+        <v>2.6791</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3946</v>
+        <v>-2.8138</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.3499</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5362</v>
+        <v>-2.4639</v>
       </c>
       <c r="P20" t="n">
         <v>-3.4801</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.4377</v>
+        <v>-4.7852</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1219</v>
+        <v>0.3897</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>0.0421</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5739</v>
+        <v>0.3476</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1915</v>
+        <v>0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6264999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2834</v>
+        <v>-4.2448</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5408</v>
+        <v>-4.3173</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2575</v>
+        <v>0.0725</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2387</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3444</v>
+        <v>-0.3058</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2036</v>
+        <v>0.0186</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0477</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5467</v>
+        <v>-4.354</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8089</v>
+        <v>-0.5854</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7378</v>
+        <v>-3.7686</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4183</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6286</v>
+        <v>-0.4359</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0806</v>
+        <v>-0.1115</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5163</v>
+        <v>2.5165</v>
       </c>
       <c r="E23" t="n">
-        <v>7.636899999999999</v>
+        <v>7.637</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1203</v>
+        <v>-5.120500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>3.538000000000001</v>
@@ -2218,7 +2218,7 @@
         <v>1.824799999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.713199999999999</v>
+        <v>1.7132</v>
       </c>
       <c r="J23" t="n">
         <v>19.5802</v>
@@ -2248,13 +2248,13 @@
         <v>16.313</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5828</v>
+        <v>-0.5827000000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.667</v>
+        <v>-0.6669</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0842</v>
+        <v>0.08409999999999994</v>
       </c>
       <c r="V23" t="n">
         <v>1.7365</v>
